--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/155.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/155.xlsx
@@ -426,13 +426,13 @@
         <v>-13.28166267485501</v>
       </c>
       <c r="E2">
-        <v>-8.013580623733052</v>
+        <v>-6.660558631247294</v>
       </c>
       <c r="F2">
-        <v>-1.366167132218099</v>
+        <v>-1.672333119055641</v>
       </c>
       <c r="G2">
-        <v>-9.842928390211584</v>
+        <v>-10.13978831926357</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-12.69009165137175</v>
       </c>
       <c r="E3">
-        <v>-8.465119295511871</v>
+        <v>-7.061346694822151</v>
       </c>
       <c r="F3">
-        <v>-1.219584855655728</v>
+        <v>-1.833378589890763</v>
       </c>
       <c r="G3">
-        <v>-9.633208640844295</v>
+        <v>-9.870005342177283</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-12.04118366532924</v>
       </c>
       <c r="E4">
-        <v>-9.35841513521294</v>
+        <v>-8.438192989062262</v>
       </c>
       <c r="F4">
-        <v>-1.318121454008455</v>
+        <v>-1.339811098373356</v>
       </c>
       <c r="G4">
-        <v>-9.316031893817801</v>
+        <v>-9.60292377025104</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-11.39338209345836</v>
       </c>
       <c r="E5">
-        <v>-9.771928210749351</v>
+        <v>-8.386224221350238</v>
       </c>
       <c r="F5">
-        <v>-1.248786017177558</v>
+        <v>-1.515036280122365</v>
       </c>
       <c r="G5">
-        <v>-8.81386848314791</v>
+        <v>-9.675828604116871</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-10.75035349093637</v>
       </c>
       <c r="E6">
-        <v>-9.912455816155378</v>
+        <v>-9.455075412906664</v>
       </c>
       <c r="F6">
-        <v>-0.7587375202042566</v>
+        <v>-1.191977694137787</v>
       </c>
       <c r="G6">
-        <v>-9.02118808699923</v>
+        <v>-9.863778206017914</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-10.11657944549156</v>
       </c>
       <c r="E7">
-        <v>-10.6426586644702</v>
+        <v>-10.00107805248549</v>
       </c>
       <c r="F7">
-        <v>-0.5926218148808552</v>
+        <v>-0.9155410347448739</v>
       </c>
       <c r="G7">
-        <v>-8.966087367043601</v>
+        <v>-9.072266494124644</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-9.505671965170308</v>
       </c>
       <c r="E8">
-        <v>-10.79617846180423</v>
+        <v>-11.22139764265047</v>
       </c>
       <c r="F8">
-        <v>-0.2716315488218417</v>
+        <v>-0.7099403735377363</v>
       </c>
       <c r="G8">
-        <v>-9.105117037510833</v>
+        <v>-9.780647096981275</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-8.916374496892557</v>
       </c>
       <c r="E9">
-        <v>-11.922500516992</v>
+        <v>-11.34612993071774</v>
       </c>
       <c r="F9">
-        <v>0.06027995323004232</v>
+        <v>-0.6602769397354706</v>
       </c>
       <c r="G9">
-        <v>-8.833115994913234</v>
+        <v>-8.900796787918093</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-8.363698219340742</v>
       </c>
       <c r="E10">
-        <v>-12.28243268806966</v>
+        <v>-11.24596008566808</v>
       </c>
       <c r="F10">
-        <v>0.1636745694783798</v>
+        <v>-0.5976239500147706</v>
       </c>
       <c r="G10">
-        <v>-7.968980845524972</v>
+        <v>-7.700210895373702</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-7.841419745747118</v>
       </c>
       <c r="E11">
-        <v>-13.25418886842763</v>
+        <v>-12.80572955897402</v>
       </c>
       <c r="F11">
-        <v>0.4557360714330186</v>
+        <v>-0.1913091522025837</v>
       </c>
       <c r="G11">
-        <v>-8.944340393396127</v>
+        <v>-7.837962695262775</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-7.363056678071787</v>
       </c>
       <c r="E12">
-        <v>-13.22420584202284</v>
+        <v>-14.47237101886099</v>
       </c>
       <c r="F12">
-        <v>0.7775870816570735</v>
+        <v>-0.2019825382196879</v>
       </c>
       <c r="G12">
-        <v>-8.078073252680575</v>
+        <v>-9.256137503921305</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-6.919856587583445</v>
       </c>
       <c r="E13">
-        <v>-14.04956551466084</v>
+        <v>-14.07093085502903</v>
       </c>
       <c r="F13">
-        <v>0.9883292441186854</v>
+        <v>0.2085132432092592</v>
       </c>
       <c r="G13">
-        <v>-8.050986369078258</v>
+        <v>-7.641260010955899</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-6.524228234138362</v>
       </c>
       <c r="E14">
-        <v>-14.52237442885369</v>
+        <v>-15.73768099829218</v>
       </c>
       <c r="F14">
-        <v>1.272029570692762</v>
+        <v>0.5204716344325215</v>
       </c>
       <c r="G14">
-        <v>-7.401334844088298</v>
+        <v>-8.167236175689766</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-6.169238554042297</v>
       </c>
       <c r="E15">
-        <v>-16.6549188800718</v>
+        <v>-15.57477367434025</v>
       </c>
       <c r="F15">
-        <v>1.299660487799434</v>
+        <v>0.4813335101442665</v>
       </c>
       <c r="G15">
-        <v>-6.692878098684265</v>
+        <v>-7.151944827523922</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-5.864980105339878</v>
       </c>
       <c r="E16">
-        <v>-16.61691139772543</v>
+        <v>-16.86283470718597</v>
       </c>
       <c r="F16">
-        <v>1.415209255095811</v>
+        <v>0.7689289614173661</v>
       </c>
       <c r="G16">
-        <v>-7.204105783040678</v>
+        <v>-6.370106529696402</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-5.607647040178428</v>
       </c>
       <c r="E17">
-        <v>-16.86360907624129</v>
+        <v>-18.20171427534578</v>
       </c>
       <c r="F17">
-        <v>2.198087351392739</v>
+        <v>1.230150051464881</v>
       </c>
       <c r="G17">
-        <v>-6.985328381077942</v>
+        <v>-7.018129266281041</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-5.402364592890092</v>
       </c>
       <c r="E18">
-        <v>-17.7281808053117</v>
+        <v>-18.4530536397195</v>
       </c>
       <c r="F18">
-        <v>2.395965070703237</v>
+        <v>1.558428532146747</v>
       </c>
       <c r="G18">
-        <v>-7.032238811369415</v>
+        <v>-5.83947573793432</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-5.24443801666581</v>
       </c>
       <c r="E19">
-        <v>-19.72330418429305</v>
+        <v>-18.18999005613992</v>
       </c>
       <c r="F19">
-        <v>2.719015738158237</v>
+        <v>1.950402081041672</v>
       </c>
       <c r="G19">
-        <v>-7.42281366354709</v>
+        <v>-6.046470908322791</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-5.132126997239983</v>
       </c>
       <c r="E20">
-        <v>-19.23273006656812</v>
+        <v>-19.7431117296026</v>
       </c>
       <c r="F20">
-        <v>3.078391868195672</v>
+        <v>2.263142822987161</v>
       </c>
       <c r="G20">
-        <v>-6.308629699032136</v>
+        <v>-6.015745735172814</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-5.059096961085689</v>
       </c>
       <c r="E21">
-        <v>-20.01384654815118</v>
+        <v>-21.07492234983643</v>
       </c>
       <c r="F21">
-        <v>3.269079562650074</v>
+        <v>2.430046422003494</v>
       </c>
       <c r="G21">
-        <v>-6.166988008134418</v>
+        <v>-5.258637212523651</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-5.018351933266139</v>
       </c>
       <c r="E22">
-        <v>-20.53732455801585</v>
+        <v>-20.47444216794534</v>
       </c>
       <c r="F22">
-        <v>3.363826352747154</v>
+        <v>2.651804842812902</v>
       </c>
       <c r="G22">
-        <v>-6.254992240204865</v>
+        <v>-4.853452922881172</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-5.005777748716934</v>
       </c>
       <c r="E23">
-        <v>-21.50932074749622</v>
+        <v>-21.52663310362754</v>
       </c>
       <c r="F23">
-        <v>3.469201393242749</v>
+        <v>2.573137418875278</v>
       </c>
       <c r="G23">
-        <v>-5.858173699140123</v>
+        <v>-4.677239204916845</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-5.014971198426781</v>
       </c>
       <c r="E24">
-        <v>-21.09757830529681</v>
+        <v>-21.96660605279077</v>
       </c>
       <c r="F24">
-        <v>3.795337119821025</v>
+        <v>2.791566889850433</v>
       </c>
       <c r="G24">
-        <v>-5.179770086141594</v>
+        <v>-5.199385068461775</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-5.046391913127957</v>
       </c>
       <c r="E25">
-        <v>-21.90163603620272</v>
+        <v>-21.43022189200424</v>
       </c>
       <c r="F25">
-        <v>3.912065748024405</v>
+        <v>3.047641050435584</v>
       </c>
       <c r="G25">
-        <v>-5.652860285885604</v>
+        <v>-5.578144583609792</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-5.093020283245855</v>
       </c>
       <c r="E26">
-        <v>-22.28349054995151</v>
+        <v>-22.27819223536254</v>
       </c>
       <c r="F26">
-        <v>3.595004656341597</v>
+        <v>3.048082904385992</v>
       </c>
       <c r="G26">
-        <v>-4.861153251805517</v>
+        <v>-5.320862226479792</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-5.158704089965385</v>
       </c>
       <c r="E27">
-        <v>-21.33995129113534</v>
+        <v>-21.9431847852231</v>
       </c>
       <c r="F27">
-        <v>3.845429737926375</v>
+        <v>2.894108680463307</v>
       </c>
       <c r="G27">
-        <v>-5.360843684957571</v>
+        <v>-4.747545260534348</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-5.237186813550484</v>
       </c>
       <c r="E28">
-        <v>-22.73699910792367</v>
+        <v>-22.24111309018773</v>
       </c>
       <c r="F28">
-        <v>3.671765298357031</v>
+        <v>3.023812611231882</v>
       </c>
       <c r="G28">
-        <v>-4.280821239862356</v>
+        <v>-5.300009100127923</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-5.33362112340805</v>
       </c>
       <c r="E29">
-        <v>-21.18030899694294</v>
+        <v>-22.99422548850736</v>
       </c>
       <c r="F29">
-        <v>3.645805190991148</v>
+        <v>2.944164873332602</v>
       </c>
       <c r="G29">
-        <v>-5.248477148263627</v>
+        <v>-5.027475059698501</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-5.439902156104486</v>
       </c>
       <c r="E30">
-        <v>-21.16886554312556</v>
+        <v>-22.27765334695563</v>
       </c>
       <c r="F30">
-        <v>3.43778066788043</v>
+        <v>2.566580876385359</v>
       </c>
       <c r="G30">
-        <v>-4.723672916650663</v>
+        <v>-4.522924745694797</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-5.559245550752719</v>
       </c>
       <c r="E31">
-        <v>-22.00032507025189</v>
+        <v>-21.63168011518347</v>
       </c>
       <c r="F31">
-        <v>3.628256145742164</v>
+        <v>2.606768997695551</v>
       </c>
       <c r="G31">
-        <v>-5.150190361748205</v>
+        <v>-4.649089636196422</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-5.681120439912542</v>
       </c>
       <c r="E32">
-        <v>-21.05322643086568</v>
+        <v>-21.67349151569629</v>
       </c>
       <c r="F32">
-        <v>3.412004270400738</v>
+        <v>2.753195279225251</v>
       </c>
       <c r="G32">
-        <v>-4.965720143208936</v>
+        <v>-5.160962876932994</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-5.809453769779194</v>
       </c>
       <c r="E33">
-        <v>-20.86078439943573</v>
+        <v>-20.80724425124304</v>
       </c>
       <c r="F33">
-        <v>3.591035889317506</v>
+        <v>2.808279738376066</v>
       </c>
       <c r="G33">
-        <v>-5.639551892817733</v>
+        <v>-4.674226608476109</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-5.935854851878761</v>
       </c>
       <c r="E34">
-        <v>-19.94885388919309</v>
+        <v>-21.54065325915529</v>
       </c>
       <c r="F34">
-        <v>3.042147174614925</v>
+        <v>2.564138801863752</v>
       </c>
       <c r="G34">
-        <v>-4.657763265509312</v>
+        <v>-4.595081396268752</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-6.068460198928713</v>
       </c>
       <c r="E35">
-        <v>-19.44839411270941</v>
+        <v>-19.66009121561998</v>
       </c>
       <c r="F35">
-        <v>3.040457360403151</v>
+        <v>2.288718089815593</v>
       </c>
       <c r="G35">
-        <v>-5.047788567127469</v>
+        <v>-5.262288744253467</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-6.203296808520081</v>
       </c>
       <c r="E36">
-        <v>-20.42483726366531</v>
+        <v>-20.52216775551218</v>
       </c>
       <c r="F36">
-        <v>3.145371542477352</v>
+        <v>2.083949666067018</v>
       </c>
       <c r="G36">
-        <v>-5.377412965381622</v>
+        <v>-4.421959727838105</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-6.353854004606077</v>
       </c>
       <c r="E37">
-        <v>-18.80363904044532</v>
+        <v>-19.55196031326483</v>
       </c>
       <c r="F37">
-        <v>3.13678468900384</v>
+        <v>2.188740319079816</v>
       </c>
       <c r="G37">
-        <v>-4.99904740515278</v>
+        <v>-4.799686352777869</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-6.52071544929537</v>
       </c>
       <c r="E38">
-        <v>-19.4077691723866</v>
+        <v>-19.1987121698225</v>
       </c>
       <c r="F38">
-        <v>2.688711525466303</v>
+        <v>1.783557079144211</v>
       </c>
       <c r="G38">
-        <v>-5.047748840580998</v>
+        <v>-5.594482125846095</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-6.720288172720011</v>
       </c>
       <c r="E39">
-        <v>-18.42480049038564</v>
+        <v>-19.554419274651</v>
       </c>
       <c r="F39">
-        <v>2.966756438216345</v>
+        <v>2.25322565654468</v>
       </c>
       <c r="G39">
-        <v>-5.042458588809242</v>
+        <v>-4.429570672032889</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-6.952294649651487</v>
       </c>
       <c r="E40">
-        <v>-18.24183655505373</v>
+        <v>-18.69815729538465</v>
       </c>
       <c r="F40">
-        <v>2.740805947848768</v>
+        <v>2.053233689837071</v>
       </c>
       <c r="G40">
-        <v>-5.270515449918556</v>
+        <v>-4.163171072487737</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-7.228271986206908</v>
       </c>
       <c r="E41">
-        <v>-17.84785478791241</v>
+        <v>-18.82898490946625</v>
       </c>
       <c r="F41">
-        <v>2.964985855002884</v>
+        <v>1.868838058984709</v>
       </c>
       <c r="G41">
-        <v>-4.945270903412858</v>
+        <v>-4.699754225129428</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-7.541135782983849</v>
       </c>
       <c r="E42">
-        <v>-17.95215460125707</v>
+        <v>-17.3639148846087</v>
       </c>
       <c r="F42">
-        <v>2.926842298029525</v>
+        <v>1.898920552848482</v>
       </c>
       <c r="G42">
-        <v>-5.640621199026918</v>
+        <v>-4.412981528335601</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-7.894803434411116</v>
       </c>
       <c r="E43">
-        <v>-16.91660127907904</v>
+        <v>-17.72743813557444</v>
       </c>
       <c r="F43">
-        <v>2.954468464018451</v>
+        <v>2.129771029318428</v>
       </c>
       <c r="G43">
-        <v>-4.671651004046556</v>
+        <v>-3.805542769516888</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-8.275751372474415</v>
       </c>
       <c r="E44">
-        <v>-15.48796282761321</v>
+        <v>-16.16613803805391</v>
       </c>
       <c r="F44">
-        <v>2.89573989755621</v>
+        <v>1.810248858643027</v>
       </c>
       <c r="G44">
-        <v>-4.421562462373392</v>
+        <v>-3.833305004409216</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-8.680419347978114</v>
       </c>
       <c r="E45">
-        <v>-15.94270765898946</v>
+        <v>-16.1093419170497</v>
       </c>
       <c r="F45">
-        <v>2.784500394055743</v>
+        <v>2.004195819871403</v>
       </c>
       <c r="G45">
-        <v>-4.650787946058069</v>
+        <v>-3.599461309697257</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-9.089336153761545</v>
       </c>
       <c r="E46">
-        <v>-15.29039003513256</v>
+        <v>-14.75885134153423</v>
       </c>
       <c r="F46">
-        <v>2.916833276643947</v>
+        <v>1.894001562275127</v>
       </c>
       <c r="G46">
-        <v>-5.193975637050606</v>
+        <v>-4.178392960877305</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-9.493697120635574</v>
       </c>
       <c r="E47">
-        <v>-14.06693221248026</v>
+        <v>-14.94988954602182</v>
       </c>
       <c r="F47">
-        <v>2.685279634747546</v>
+        <v>1.702051654206119</v>
       </c>
       <c r="G47">
-        <v>-5.54190735213693</v>
+        <v>-4.59223101655944</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-9.874838009512588</v>
       </c>
       <c r="E48">
-        <v>-14.29116413144406</v>
+        <v>-14.30801005475259</v>
       </c>
       <c r="F48">
-        <v>2.392262366272939</v>
+        <v>1.88339865117126</v>
       </c>
       <c r="G48">
-        <v>-5.225952196414426</v>
+        <v>-4.738821973038368</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-10.2244383581331</v>
       </c>
       <c r="E49">
-        <v>-13.4111548344815</v>
+        <v>-13.28041778988005</v>
       </c>
       <c r="F49">
-        <v>2.340541698486518</v>
+        <v>1.643793448400764</v>
       </c>
       <c r="G49">
-        <v>-4.679496996974628</v>
+        <v>-5.191800608631305</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-10.52896000043745</v>
       </c>
       <c r="E50">
-        <v>-12.08822908025072</v>
+        <v>-13.27736559839888</v>
       </c>
       <c r="F50">
-        <v>2.760162001547269</v>
+        <v>1.95106248640841</v>
       </c>
       <c r="G50">
-        <v>-4.832821603080434</v>
+        <v>-4.800712621895043</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-10.78216794885763</v>
       </c>
       <c r="E51">
-        <v>-13.00889048838014</v>
+        <v>-13.12682100848789</v>
       </c>
       <c r="F51">
-        <v>2.413103936120122</v>
+        <v>1.278847424658728</v>
       </c>
       <c r="G51">
-        <v>-4.927354230954323</v>
+        <v>-4.831441105590558</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-10.97806162379065</v>
       </c>
       <c r="E52">
-        <v>-13.01738590561853</v>
+        <v>-13.30867546768792</v>
       </c>
       <c r="F52">
-        <v>2.144757638396232</v>
+        <v>1.446843780756714</v>
       </c>
       <c r="G52">
-        <v>-5.156738620824884</v>
+        <v>-5.071213987363352</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-11.11537511811309</v>
       </c>
       <c r="E53">
-        <v>-12.30298743159048</v>
+        <v>-13.12650401530735</v>
       </c>
       <c r="F53">
-        <v>2.258683107129284</v>
+        <v>1.293727925440197</v>
       </c>
       <c r="G53">
-        <v>-4.793926003539537</v>
+        <v>-4.222830413650943</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-11.1974247635391</v>
       </c>
       <c r="E54">
-        <v>-10.84689284221613</v>
+        <v>-12.21571920898866</v>
       </c>
       <c r="F54">
-        <v>2.101156630838268</v>
+        <v>1.34487529168523</v>
       </c>
       <c r="G54">
-        <v>-5.530926272583167</v>
+        <v>-4.907358535897124</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-11.2274576514401</v>
       </c>
       <c r="E55">
-        <v>-11.60651265768478</v>
+        <v>-11.2528207237897</v>
       </c>
       <c r="F55">
-        <v>2.071745628282642</v>
+        <v>1.082733953738031</v>
       </c>
       <c r="G55">
-        <v>-4.990032789649344</v>
+        <v>-4.456220563624022</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-11.21610325734331</v>
       </c>
       <c r="E56">
-        <v>-11.38278792780983</v>
+        <v>-10.13095468702547</v>
       </c>
       <c r="F56">
-        <v>2.104178341724927</v>
+        <v>1.033594726593776</v>
       </c>
       <c r="G56">
-        <v>-5.270194327001247</v>
+        <v>-4.522040830035812</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-11.16745066582211</v>
       </c>
       <c r="E57">
-        <v>-10.6859961607236</v>
+        <v>-10.26198155396341</v>
       </c>
       <c r="F57">
-        <v>1.863483549284608</v>
+        <v>1.612402813450839</v>
       </c>
       <c r="G57">
-        <v>-5.83120930572276</v>
+        <v>-4.369408127947714</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-11.09449675061675</v>
       </c>
       <c r="E58">
-        <v>-10.32427071393891</v>
+        <v>-10.22628812183495</v>
       </c>
       <c r="F58">
-        <v>1.890111980546807</v>
+        <v>1.300140350691812</v>
       </c>
       <c r="G58">
-        <v>-5.408614857089254</v>
+        <v>-5.333733627536478</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-10.996984900432</v>
       </c>
       <c r="E59">
-        <v>-10.28034904453852</v>
+        <v>-9.325384445800992</v>
       </c>
       <c r="F59">
-        <v>1.655139117578972</v>
+        <v>1.177138663357376</v>
       </c>
       <c r="G59">
-        <v>-4.940824840753617</v>
+        <v>-4.868512594539316</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-10.88638662853371</v>
       </c>
       <c r="E60">
-        <v>-11.08287615122984</v>
+        <v>-9.052779367487252</v>
       </c>
       <c r="F60">
-        <v>1.755096300137848</v>
+        <v>1.036494492124945</v>
       </c>
       <c r="G60">
-        <v>-5.716462486786082</v>
+        <v>-4.823962583217345</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-10.75790433420885</v>
       </c>
       <c r="E61">
-        <v>-10.06988368655803</v>
+        <v>-9.513583297085765</v>
       </c>
       <c r="F61">
-        <v>1.505710129633598</v>
+        <v>1.004733269990807</v>
       </c>
       <c r="G61">
-        <v>-5.305908492278904</v>
+        <v>-5.823717541167389</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-10.62090493561595</v>
       </c>
       <c r="E62">
-        <v>-9.548715198437272</v>
+        <v>-9.392039054719893</v>
       </c>
       <c r="F62">
-        <v>1.540508899713549</v>
+        <v>0.6024767185869339</v>
       </c>
       <c r="G62">
-        <v>-5.325738660059138</v>
+        <v>-5.361509104610964</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-10.46612564411175</v>
       </c>
       <c r="E63">
-        <v>-9.769269996506848</v>
+        <v>-8.941618916020968</v>
       </c>
       <c r="F63">
-        <v>1.269864644706356</v>
+        <v>0.6677808320100794</v>
       </c>
       <c r="G63">
-        <v>-5.348002078810738</v>
+        <v>-5.618821256650817</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-10.29892181588803</v>
       </c>
       <c r="E64">
-        <v>-9.174387008489232</v>
+        <v>-7.981958289737489</v>
       </c>
       <c r="F64">
-        <v>1.22239939471472</v>
+        <v>0.3795043871933408</v>
       </c>
       <c r="G64">
-        <v>-5.381627289853115</v>
+        <v>-4.25204928858055</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-10.10657003234393</v>
       </c>
       <c r="E65">
-        <v>-8.875299414178636</v>
+        <v>-8.254871304283752</v>
       </c>
       <c r="F65">
-        <v>1.351601290708101</v>
+        <v>0.6600396774954114</v>
       </c>
       <c r="G65">
-        <v>-5.337802288004243</v>
+        <v>-4.921385317347017</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-9.891933088713872</v>
       </c>
       <c r="E66">
-        <v>-8.893598977643633</v>
+        <v>-8.853716707058078</v>
       </c>
       <c r="F66">
-        <v>1.262882085325183</v>
+        <v>0.4431717405528798</v>
       </c>
       <c r="G66">
-        <v>-4.652933179567516</v>
+        <v>-5.412825871015206</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-9.64103740872017</v>
       </c>
       <c r="E67">
-        <v>-9.113882067272749</v>
+        <v>-8.431649344121178</v>
       </c>
       <c r="F67">
-        <v>1.151929232595411</v>
+        <v>0.6255038025974233</v>
       </c>
       <c r="G67">
-        <v>-5.782329100835421</v>
+        <v>-4.838817001052054</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-9.356915762502057</v>
       </c>
       <c r="E68">
-        <v>-8.338358251089161</v>
+        <v>-7.118713403551319</v>
       </c>
       <c r="F68">
-        <v>1.081322871767374</v>
+        <v>-0.01963543096894764</v>
       </c>
       <c r="G68">
-        <v>-4.879675754097739</v>
+        <v>-5.623906254599137</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.027709329701349</v>
       </c>
       <c r="E69">
-        <v>-9.158519235566356</v>
+        <v>-7.883473037018674</v>
       </c>
       <c r="F69">
-        <v>0.90574531545218</v>
+        <v>0.1960360161544695</v>
       </c>
       <c r="G69">
-        <v>-5.064966987930747</v>
+        <v>-5.008015673018665</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-8.65957213914535</v>
       </c>
       <c r="E70">
-        <v>-8.2238467288572</v>
+        <v>-9.096103278318635</v>
       </c>
       <c r="F70">
-        <v>0.7165621416174452</v>
+        <v>-0.3588034735253751</v>
       </c>
       <c r="G70">
-        <v>-5.53704416073974</v>
+        <v>-4.675011207768915</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-8.24438986347494</v>
       </c>
       <c r="E71">
-        <v>-7.494898267842504</v>
+        <v>-7.869276271004628</v>
       </c>
       <c r="F71">
-        <v>1.088183485793058</v>
+        <v>0.0972990790034394</v>
       </c>
       <c r="G71">
-        <v>-4.748746988565102</v>
+        <v>-4.865940300655303</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-7.792030145583386</v>
       </c>
       <c r="E72">
-        <v>-9.006072686572141</v>
+        <v>-8.819010482263293</v>
       </c>
       <c r="F72">
-        <v>0.5024633144680596</v>
+        <v>-0.1241014242690799</v>
       </c>
       <c r="G72">
-        <v>-4.607317172581898</v>
+        <v>-4.182200088247467</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-7.298555315625238</v>
       </c>
       <c r="E73">
-        <v>-9.411398281102683</v>
+        <v>-8.365610607667321</v>
       </c>
       <c r="F73">
-        <v>0.3651029574512922</v>
+        <v>-0.06161789108133195</v>
       </c>
       <c r="G73">
-        <v>-4.560721244116657</v>
+        <v>-4.52077620163981</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-6.777622112027856</v>
       </c>
       <c r="E74">
-        <v>-8.946613822851429</v>
+        <v>-8.821048295566746</v>
       </c>
       <c r="F74">
-        <v>0.414568428014128</v>
+        <v>-0.3343067104253578</v>
       </c>
       <c r="G74">
-        <v>-4.649205505290297</v>
+        <v>-4.244037768375514</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-6.22832992939253</v>
       </c>
       <c r="E75">
-        <v>-9.741786687754297</v>
+        <v>-8.124587107083075</v>
       </c>
       <c r="F75">
-        <v>0.4108095020238324</v>
+        <v>-0.07939419812918203</v>
       </c>
       <c r="G75">
-        <v>-4.650453580958602</v>
+        <v>-4.117210768766035</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-5.66660558802046</v>
       </c>
       <c r="E76">
-        <v>-9.916083123835522</v>
+        <v>-9.785377778552132</v>
       </c>
       <c r="F76">
-        <v>0.2997457898799794</v>
+        <v>-0.5219877391992981</v>
       </c>
       <c r="G76">
-        <v>-4.171910912711413</v>
+        <v>-4.391602025242988</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-5.093206953552882</v>
       </c>
       <c r="E77">
-        <v>-10.5564048200461</v>
+        <v>-10.40392204325983</v>
       </c>
       <c r="F77">
-        <v>0.2255388736531909</v>
+        <v>-0.2128024170339702</v>
       </c>
       <c r="G77">
-        <v>-4.012892168278061</v>
+        <v>-4.242938667256476</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-4.525430609852029</v>
       </c>
       <c r="E78">
-        <v>-10.62971628575628</v>
+        <v>-10.52279448596117</v>
       </c>
       <c r="F78">
-        <v>0.1484638660135416</v>
+        <v>-0.5190935166388325</v>
       </c>
       <c r="G78">
-        <v>-2.967507961160241</v>
+        <v>-3.609634616139437</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.965134352990118</v>
       </c>
       <c r="E79">
-        <v>-11.79936225177543</v>
+        <v>-11.03931223127605</v>
       </c>
       <c r="F79">
-        <v>0.169920705608873</v>
+        <v>-0.6139733380328097</v>
       </c>
       <c r="G79">
-        <v>-3.196978425214823</v>
+        <v>-3.727228504239889</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.430113526346874</v>
       </c>
       <c r="E80">
-        <v>-11.1989228261504</v>
+        <v>-11.86142498805055</v>
       </c>
       <c r="F80">
-        <v>0.004911218867406075</v>
+        <v>-0.4921610138408692</v>
       </c>
       <c r="G80">
-        <v>-3.370149751828559</v>
+        <v>-2.911622641911804</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-2.92332003840048</v>
       </c>
       <c r="E81">
-        <v>-12.09174770455468</v>
+        <v>-12.38212704334852</v>
       </c>
       <c r="F81">
-        <v>0.2494845070946354</v>
+        <v>-0.8493682586271097</v>
       </c>
       <c r="G81">
-        <v>-2.916830130045077</v>
+        <v>-2.791757719571412</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.461454456454293</v>
       </c>
       <c r="E82">
-        <v>-13.69406671963669</v>
+        <v>-12.26163793542644</v>
       </c>
       <c r="F82">
-        <v>0.04086213500083925</v>
+        <v>-0.4482567266000992</v>
       </c>
       <c r="G82">
-        <v>-2.549147700271462</v>
+        <v>-2.281490093421386</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-2.048609954783021</v>
       </c>
       <c r="E83">
-        <v>-14.95195905864332</v>
+        <v>-14.75010685822542</v>
       </c>
       <c r="F83">
-        <v>0.08018000991049669</v>
+        <v>-0.9508782648360743</v>
       </c>
       <c r="G83">
-        <v>-1.993681195873767</v>
+        <v>-2.275176883077997</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-1.697718148194763</v>
       </c>
       <c r="E84">
-        <v>-15.75944484437304</v>
+        <v>-15.3776175014683</v>
       </c>
       <c r="F84">
-        <v>-0.04618546878833225</v>
+        <v>-0.7140342533291473</v>
       </c>
       <c r="G84">
-        <v>-1.379320086332438</v>
+        <v>-2.97277834965876</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-1.412296130088624</v>
       </c>
       <c r="E85">
-        <v>-15.31613893834017</v>
+        <v>-16.02205105207785</v>
       </c>
       <c r="F85">
-        <v>-0.151828155583636</v>
+        <v>-0.4008025625498716</v>
       </c>
       <c r="G85">
-        <v>-1.253297549289002</v>
+        <v>-2.432172884186854</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-1.200718559849747</v>
       </c>
       <c r="E86">
-        <v>-17.64184544835546</v>
+        <v>-16.96408685752347</v>
       </c>
       <c r="F86">
-        <v>-0.1734433657705113</v>
+        <v>-1.259734176170991</v>
       </c>
       <c r="G86">
-        <v>-1.326023613695712</v>
+        <v>-1.674723375347146</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-1.065428162480935</v>
       </c>
       <c r="E87">
-        <v>-20.50649923544563</v>
+        <v>-19.11343647578406</v>
       </c>
       <c r="F87">
-        <v>-0.6888755011564762</v>
+        <v>-0.913726899618738</v>
       </c>
       <c r="G87">
-        <v>-1.017937624720056</v>
+        <v>-0.8651162215362198</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-1.009137554254586</v>
       </c>
       <c r="E88">
-        <v>-20.85559929669694</v>
+        <v>-20.90174897530911</v>
       </c>
       <c r="F88">
-        <v>-0.3446475182002197</v>
+        <v>-1.096406585111721</v>
       </c>
       <c r="G88">
-        <v>-1.881301416997668</v>
+        <v>-1.699992769448403</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-1.031637854757016</v>
       </c>
       <c r="E89">
-        <v>-21.8903420220276</v>
+        <v>-22.32075989103464</v>
       </c>
       <c r="F89">
-        <v>-0.4353938671549</v>
+        <v>-1.138978183824648</v>
       </c>
       <c r="G89">
-        <v>-0.8356027080536171</v>
+        <v>-1.956341552736328</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-1.128668046158451</v>
       </c>
       <c r="E90">
-        <v>-23.15016349096149</v>
+        <v>-23.40461391697848</v>
       </c>
       <c r="F90">
-        <v>-0.3710930314291853</v>
+        <v>-1.095705003391181</v>
       </c>
       <c r="G90">
-        <v>-1.125050325643176</v>
+        <v>-1.95092550023408</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-1.296533615825974</v>
       </c>
       <c r="E91">
-        <v>-25.79452513147453</v>
+        <v>-24.52572369858342</v>
       </c>
       <c r="F91">
-        <v>-0.6517771900873072</v>
+        <v>-1.027785399648687</v>
       </c>
       <c r="G91">
-        <v>-0.9699976147658702</v>
+        <v>-0.8285280722361946</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-1.524431832639046</v>
       </c>
       <c r="E92">
-        <v>-27.3413793969106</v>
+        <v>-28.42328165055713</v>
       </c>
       <c r="F92">
-        <v>-0.8143675660429402</v>
+        <v>-1.205983197400976</v>
       </c>
       <c r="G92">
-        <v>-1.468300929336969</v>
+        <v>-1.835976738019506</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-1.807038625017402</v>
       </c>
       <c r="E93">
-        <v>-29.52128262930093</v>
+        <v>-28.0797742547053</v>
       </c>
       <c r="F93">
-        <v>-0.5910515704656969</v>
+        <v>-1.35291864038249</v>
       </c>
       <c r="G93">
-        <v>-0.8480669120089732</v>
+        <v>-2.078672831503477</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.131293519008626</v>
       </c>
       <c r="E94">
-        <v>-31.80703667738355</v>
+        <v>-32.43675268746817</v>
       </c>
       <c r="F94">
-        <v>-0.8343887762259258</v>
+        <v>-1.681687278045185</v>
       </c>
       <c r="G94">
-        <v>-1.725563423193733</v>
+        <v>-0.3085175105640944</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.491572036559542</v>
       </c>
       <c r="E95">
-        <v>-34.44117302358727</v>
+        <v>-34.00947586067306</v>
       </c>
       <c r="F95">
-        <v>-0.7483975042823524</v>
+        <v>-1.429471816923002</v>
       </c>
       <c r="G95">
-        <v>-1.875014691018592</v>
+        <v>-1.382405514775039</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-2.878417017359564</v>
       </c>
       <c r="E96">
-        <v>-35.50985213313141</v>
+        <v>-36.35697791608727</v>
       </c>
       <c r="F96">
-        <v>-0.5135869711708495</v>
+        <v>-1.223056339022371</v>
       </c>
       <c r="G96">
-        <v>-1.979594824604169</v>
+        <v>-1.643716805826332</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.282028699237229</v>
       </c>
       <c r="E97">
-        <v>-39.08269812062212</v>
+        <v>-38.82843109780244</v>
       </c>
       <c r="F97">
-        <v>-0.9053395930905708</v>
+        <v>-1.149672949871611</v>
       </c>
       <c r="G97">
-        <v>-2.431467737986989</v>
+        <v>-2.027402412736784</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-3.699970834819886</v>
       </c>
       <c r="E98">
-        <v>-41.20162318626216</v>
+        <v>-39.3534986020438</v>
       </c>
       <c r="F98">
-        <v>-0.8784949859709144</v>
+        <v>-1.018749565548147</v>
       </c>
       <c r="G98">
-        <v>-2.283651879658531</v>
+        <v>-2.687879421640161</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.112737732553343</v>
       </c>
       <c r="E99">
-        <v>-43.2164001424368</v>
+        <v>-43.78884001327241</v>
       </c>
       <c r="F99">
-        <v>-0.9025760262681289</v>
+        <v>-1.337783954801593</v>
       </c>
       <c r="G99">
-        <v>-2.99894159105562</v>
+        <v>-2.634083056627003</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.53319915246281</v>
       </c>
       <c r="E100">
-        <v>-45.82451134851844</v>
+        <v>-45.26583124595515</v>
       </c>
       <c r="F100">
-        <v>-1.093533742581113</v>
+        <v>-1.407280929635865</v>
       </c>
       <c r="G100">
-        <v>-2.865016781809944</v>
+        <v>-2.998100712488645</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.918714462475655</v>
       </c>
       <c r="E101">
-        <v>-48.06249452429415</v>
+        <v>-47.43516275577457</v>
       </c>
       <c r="F101">
-        <v>-0.9858884596557365</v>
+        <v>-1.404191119394842</v>
       </c>
       <c r="G101">
-        <v>-3.750097752825174</v>
+        <v>-2.729923349988904</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-5.326106736393533</v>
       </c>
       <c r="E102">
-        <v>-50.16450007892304</v>
+        <v>-49.35762110871035</v>
       </c>
       <c r="F102">
-        <v>-1.028585171135984</v>
+        <v>-1.861836993338253</v>
       </c>
       <c r="G102">
-        <v>-3.91423460066224</v>
+        <v>-2.642015123739097</v>
       </c>
     </row>
   </sheetData>
